--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>16998</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1666.47</t>
+          <t>46518</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4560.59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1666.47</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4560.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>46518</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4560.59</t>
+          <t>76038</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7454.71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4560.59</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7454.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>76038</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7454.71</t>
+          <t>85878</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8419.41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>7454.71</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8419.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,183 +201,225 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>85878</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8419.41</t>
+          <t>89158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8740.98</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>8419.41</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8740.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,183 +243,225 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>89158</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8740.98</t>
+          <t>98398</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9646.86</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>8740.98</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>9646.86</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,183 +285,225 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>98398</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9646.86</t>
+          <t>108358</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10623.33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>9646.86</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10623.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,183 +327,225 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>108358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10623.33</t>
+          <t>118318</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11599.8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>10623.33</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11599.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,183 +369,225 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>118318</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11599.8</t>
+          <t>122336</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11993.73</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>11599.8</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11993.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -411,183 +411,225 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>122336</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11993.73</t>
+          <t>132296</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12970.2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>11993.73</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12970.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,183 +453,225 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>132296</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12970.2</t>
+          <t>142256</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13946.67</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>12970.2</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13946.67</t>
         </is>
       </c>
     </row>
